--- a/StatisticalAnalyses/Raji/output/SurvivalTable_CD19_Raji_Primary.xlsx
+++ b/StatisticalAnalyses/Raji/output/SurvivalTable_CD19_Raji_Primary.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -485,7 +485,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>100% (7/7)</t>
+          <t>100% (6/6)</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>66.7% (8/12)</t>
+          <t>91.7% (11/12)</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,88 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.7% (2/12)</t>
+          <t>36.4% (4/11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E103</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ctrl</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NTC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>70% (7/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>E103</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CD19</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MGAT5WT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CD19 CAR - mock</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>52.9% (9/17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E103</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CD19</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MGAT5KO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CD19 CAR - MGAT5 KO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>43.8% (7/16)</t>
         </is>
       </c>
     </row>
